--- a/data/daily/forms_filled.xlsx
+++ b/data/daily/forms_filled.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="74">
   <si>
     <t>Action Date</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Records COUNT</t>
   </si>
   <si>
-    <t>2026-04-20</t>
+    <t>2026-04-25</t>
   </si>
   <si>
     <t>Adesh Kumar Patel</t>
@@ -43,190 +43,196 @@
     <t>publish_new_record</t>
   </si>
   <si>
-    <t>20/04/2026 10:55 PM</t>
+    <t>25/04/2026 10:20 PM</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>Suyog Laxman Kajare</t>
+  </si>
+  <si>
+    <t>25/04/2026 9:50 PM</t>
+  </si>
+  <si>
+    <t>Kishor Krushna Tegade</t>
+  </si>
+  <si>
+    <t>25/04/2026 8:54 PM</t>
+  </si>
+  <si>
+    <t>Satish Megaraj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Form	</t>
+  </si>
+  <si>
+    <t>25/04/2026 8:05 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 7:59 PM</t>
+  </si>
+  <si>
+    <t>Ankush Shelotkar</t>
+  </si>
+  <si>
+    <t>OD SURVEY</t>
+  </si>
+  <si>
+    <t>25/04/2026 7:20 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 7:19 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 7:17 PM</t>
+  </si>
+  <si>
+    <t>Akhilesh Premprakash Giri</t>
+  </si>
+  <si>
+    <t>25/04/2026 7:10 PM</t>
+  </si>
+  <si>
+    <t>Gopal  Sonkar</t>
+  </si>
+  <si>
+    <t>Ashok Soni</t>
+  </si>
+  <si>
+    <t>25/04/2026 7:06 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 6:08 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 6:07 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 6:02 PM</t>
+  </si>
+  <si>
+    <t>Suresh Gowda</t>
+  </si>
+  <si>
+    <t>25/04/2026 5:59 PM</t>
+  </si>
+  <si>
+    <t>Anish Kumar</t>
+  </si>
+  <si>
+    <t>25/04/2026 5:28 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 5:17 PM</t>
+  </si>
+  <si>
+    <t>Ganesh Bhimsen Kumbhar</t>
+  </si>
+  <si>
+    <t>25/04/2026 4:20 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 4:05 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 4:03 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 4:02 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 3:57 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 3:54 PM</t>
+  </si>
+  <si>
+    <t>Arsadur Rahaman Halder</t>
+  </si>
+  <si>
+    <t>25/04/2026 3:12 PM</t>
+  </si>
+  <si>
+    <t>Raghvendra Kumar</t>
+  </si>
+  <si>
+    <t>25/04/2026 3:08 PM</t>
+  </si>
+  <si>
+    <t>Sagar Kanubhai</t>
+  </si>
+  <si>
+    <t>25/04/2026 1:44 PM</t>
+  </si>
+  <si>
+    <t>RATAN BAHADHUR SINGH</t>
+  </si>
+  <si>
+    <t>25/04/2026 12:51 PM</t>
+  </si>
+  <si>
+    <t>RUPESH YASHWANT RANE</t>
+  </si>
+  <si>
+    <t>25/04/2026 12:45 PM</t>
+  </si>
+  <si>
+    <t>Sibayan Ghosh</t>
+  </si>
+  <si>
+    <t>25/04/2026 12:38 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 12:09 PM</t>
+  </si>
+  <si>
+    <t>25/04/2026 11:54 AM</t>
+  </si>
+  <si>
+    <t>25/04/2026 11:53 AM</t>
+  </si>
+  <si>
+    <t>25/04/2026 11:42 AM</t>
+  </si>
+  <si>
+    <t>25/04/2026 11:41 AM</t>
+  </si>
+  <si>
+    <t>25/04/2026 11:39 AM</t>
+  </si>
+  <si>
+    <t>25/04/2026 11:14 AM</t>
+  </si>
+  <si>
+    <t>25/04/2026 10:42 AM</t>
+  </si>
+  <si>
+    <t>Sandeep Kumar Singh</t>
+  </si>
+  <si>
+    <t>25/04/2026 9:13 AM</t>
+  </si>
+  <si>
+    <t>Devendra Pal Singh</t>
+  </si>
+  <si>
+    <t>Leave Form</t>
+  </si>
+  <si>
+    <t>25/04/2026 8:53 AM</t>
+  </si>
+  <si>
     <t>Vineet Rajpoot</t>
   </si>
   <si>
-    <t>20/04/2026 10:54 PM</t>
-  </si>
-  <si>
-    <t>Suresh Gowda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meeting Form	</t>
-  </si>
-  <si>
-    <t>20/04/2026 9:17 PM</t>
-  </si>
-  <si>
-    <t>Kishor Krushna Tegade</t>
-  </si>
-  <si>
-    <t>20/04/2026 8:34 PM</t>
-  </si>
-  <si>
-    <t>Afsar Ali</t>
-  </si>
-  <si>
-    <t>OD SURVEY</t>
-  </si>
-  <si>
-    <t>20/04/2026 7:42 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 7:41 PM</t>
-  </si>
-  <si>
-    <t>Satish Megaraj</t>
-  </si>
-  <si>
-    <t>Gopal  Sonkar</t>
-  </si>
-  <si>
-    <t>20/04/2026 6:55 PM</t>
-  </si>
-  <si>
-    <t>Akhilesh Premprakash Giri</t>
-  </si>
-  <si>
-    <t>20/04/2026 6:50 PM</t>
+    <t>25/04/2026 8:38 AM</t>
   </si>
   <si>
     <t>Sachin Mahade</t>
   </si>
   <si>
-    <t>20/04/2026 6:47 PM</t>
-  </si>
-  <si>
-    <t>Pradeep  Brahampal Rajoria</t>
-  </si>
-  <si>
-    <t>20/04/2026 5:58 PM</t>
-  </si>
-  <si>
-    <t>RUPESH YASHWANT RANE</t>
-  </si>
-  <si>
-    <t>20/04/2026 5:52 PM</t>
-  </si>
-  <si>
-    <t>Sibayan Ghosh</t>
-  </si>
-  <si>
-    <t>20/04/2026 5:09 PM</t>
-  </si>
-  <si>
-    <t>Abhiman Ganguly</t>
-  </si>
-  <si>
-    <t>20/04/2026 5:04 PM</t>
-  </si>
-  <si>
-    <t>Sushank Rajendra Mohakar</t>
-  </si>
-  <si>
-    <t>20/04/2026 5:02 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 4:49 PM</t>
-  </si>
-  <si>
-    <t>Sagar Deepak Gurav</t>
-  </si>
-  <si>
-    <t>20/04/2026 4:47 PM</t>
-  </si>
-  <si>
-    <t>Arsadur Rahaman Halder</t>
-  </si>
-  <si>
-    <t>20/04/2026 2:36 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deepanshu Pandey </t>
-  </si>
-  <si>
-    <t>20/04/2026 2:15 PM</t>
-  </si>
-  <si>
-    <t>Niranjan M</t>
-  </si>
-  <si>
-    <t>20/04/2026 2:12 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 2:08 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 2:06 PM</t>
-  </si>
-  <si>
-    <t>Ganesh Bhimsen Kumbhar</t>
-  </si>
-  <si>
-    <t>20/04/2026 2:03 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 1:44 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 1:26 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 12:54 PM</t>
-  </si>
-  <si>
-    <t>Mohd Ishhanque khan</t>
-  </si>
-  <si>
-    <t>20/04/2026 12:30 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 12:09 PM</t>
-  </si>
-  <si>
-    <t>20/04/2026 11:48 AM</t>
-  </si>
-  <si>
-    <t>20/04/2026 11:32 AM</t>
-  </si>
-  <si>
-    <t>20/04/2026 11:11 AM</t>
-  </si>
-  <si>
-    <t>Karim Khan</t>
-  </si>
-  <si>
-    <t>20/04/2026 10:59 AM</t>
-  </si>
-  <si>
-    <t>Anish Kumar</t>
-  </si>
-  <si>
-    <t>20/04/2026 10:58 AM</t>
-  </si>
-  <si>
-    <t>Shivanshu Dubey</t>
-  </si>
-  <si>
-    <t>20/04/2026 9:54 AM</t>
-  </si>
-  <si>
-    <t>Nilesh K Salunke</t>
-  </si>
-  <si>
-    <t>20/04/2026 9:47 AM</t>
-  </si>
-  <si>
-    <t>Irrappa Bassapa</t>
-  </si>
-  <si>
-    <t>20/04/2026 9:27 AM</t>
+    <t>25/04/2026 12:50 AM</t>
   </si>
 </sst>
 </file>
@@ -639,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" defaultColWidth="20"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -710,13 +716,13 @@
         <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
@@ -727,10 +733,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>9</v>
@@ -747,16 +753,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>11</v>
@@ -767,10 +773,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>9</v>
@@ -787,16 +793,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>11</v>
@@ -807,16 +813,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -827,7 +833,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>8</v>
@@ -836,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>11</v>
@@ -847,7 +853,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>8</v>
@@ -856,7 +862,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -867,16 +873,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>11</v>
@@ -887,16 +893,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -907,16 +913,16 @@
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>11</v>
@@ -927,16 +933,16 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -947,16 +953,16 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>11</v>
@@ -967,16 +973,16 @@
         <v>6</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -987,16 +993,16 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>11</v>
@@ -1007,16 +1013,16 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -1027,16 +1033,16 @@
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>11</v>
@@ -1047,16 +1053,16 @@
         <v>6</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -1067,16 +1073,16 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>11</v>
@@ -1087,16 +1093,16 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -1107,16 +1113,16 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>11</v>
@@ -1127,16 +1133,16 @@
         <v>6</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -1147,16 +1153,16 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>11</v>
@@ -1167,16 +1173,16 @@
         <v>6</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -1187,16 +1193,16 @@
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>11</v>
@@ -1207,16 +1213,16 @@
         <v>6</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -1227,16 +1233,16 @@
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>11</v>
@@ -1247,16 +1253,16 @@
         <v>6</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -1267,16 +1273,16 @@
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>11</v>
@@ -1287,16 +1293,16 @@
         <v>6</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -1307,16 +1313,16 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>11</v>
@@ -1327,16 +1333,16 @@
         <v>6</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -1347,16 +1353,16 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>11</v>
@@ -1367,18 +1373,138 @@
         <v>6</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F42" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>11</v>
       </c>
     </row>
